--- a/EasyBuyConstants.xlsx
+++ b/EasyBuyConstants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Surround\AcceleratorOpenGenerationWizardPlugin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56C9A89-03AF-4F5A-B46D-E5C4BEA224BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E450FA0-22EB-4AB0-9D6B-35910921CF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D7846FDF-0C96-4653-AF05-F487C80BBA80}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{D7846FDF-0C96-4653-AF05-F487C80BBA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{59EF155A-B474-45A4-BFC9-A0E15A5DE1FE}" name="Table1" displayName="Table1" ref="B3:C9" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{59EF155A-B474-45A4-BFC9-A0E15A5DE1FE}" name="AuditStamps" displayName="AuditStamps" ref="B3:C9" totalsRowShown="0">
   <autoFilter ref="B3:C9" xr:uid="{59EF155A-B474-45A4-BFC9-A0E15A5DE1FE}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{22A90EBE-7881-4560-93D8-DC0E0B5909CC}" name="System Name"/>
